--- a/io_odds_only_pdl1_interaction.xlsx
+++ b/io_odds_only_pdl1_interaction.xlsx
@@ -666,22 +666,22 @@
         <v>7</v>
       </c>
       <c r="B2" s="32">
-        <v>1.264089</v>
+        <v>4.5175099999999997</v>
       </c>
       <c r="C2" s="33">
-        <v>0.0258169</v>
+        <v>0.2202113</v>
       </c>
       <c r="D2" s="34">
-        <v>11.470000000000001</v>
+        <v>30.93</v>
       </c>
       <c r="E2" s="35">
         <v>0</v>
       </c>
       <c r="F2" s="36">
-        <v>1.2144889999999999</v>
+        <v>4.10588</v>
       </c>
       <c r="G2" s="37">
-        <v>1.3157160000000001</v>
+        <v>4.9704059999999997</v>
       </c>
     </row>
   </sheetData>

--- a/io_odds_only_pdl1_interaction.xlsx
+++ b/io_odds_only_pdl1_interaction.xlsx
@@ -666,22 +666,22 @@
         <v>7</v>
       </c>
       <c r="B2" s="32">
-        <v>4.5175099999999997</v>
+        <v>1.1334820000000001</v>
       </c>
       <c r="C2" s="33">
-        <v>0.2202113</v>
+        <v>0.036673900000000002</v>
       </c>
       <c r="D2" s="34">
-        <v>30.93</v>
+        <v>3.8700000000000001</v>
       </c>
       <c r="E2" s="35">
         <v>0</v>
       </c>
       <c r="F2" s="36">
-        <v>4.10588</v>
+        <v>1.063834</v>
       </c>
       <c r="G2" s="37">
-        <v>4.9704059999999997</v>
+        <v>1.207689</v>
       </c>
     </row>
   </sheetData>

--- a/io_odds_only_pdl1_interaction.xlsx
+++ b/io_odds_only_pdl1_interaction.xlsx
@@ -666,22 +666,22 @@
         <v>7</v>
       </c>
       <c r="B2" s="32">
-        <v>1.1334820000000001</v>
+        <v>1.8311219999999999</v>
       </c>
       <c r="C2" s="33">
-        <v>0.036673900000000002</v>
+        <v>0.033310899999999998</v>
       </c>
       <c r="D2" s="34">
-        <v>3.8700000000000001</v>
+        <v>33.25</v>
       </c>
       <c r="E2" s="35">
         <v>0</v>
       </c>
       <c r="F2" s="36">
-        <v>1.063834</v>
+        <v>1.7669840000000001</v>
       </c>
       <c r="G2" s="37">
-        <v>1.207689</v>
+        <v>1.8975880000000001</v>
       </c>
     </row>
   </sheetData>

--- a/io_odds_only_pdl1_interaction.xlsx
+++ b/io_odds_only_pdl1_interaction.xlsx
@@ -666,22 +666,22 @@
         <v>7</v>
       </c>
       <c r="B2" s="32">
-        <v>1.8311219999999999</v>
+        <v>0.70446149999999996</v>
       </c>
       <c r="C2" s="33">
-        <v>0.033310899999999998</v>
+        <v>0.0184719</v>
       </c>
       <c r="D2" s="34">
-        <v>33.25</v>
+        <v>-13.359999999999999</v>
       </c>
       <c r="E2" s="35">
         <v>0</v>
       </c>
       <c r="F2" s="36">
-        <v>1.7669840000000001</v>
+        <v>0.66917170000000004</v>
       </c>
       <c r="G2" s="37">
-        <v>1.8975880000000001</v>
+        <v>0.7416123</v>
       </c>
     </row>
   </sheetData>
